--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D4981D-4AA0-4D43-A1CE-109473FC2610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FFBFDF-1468-429D-97E8-DD429B2D1737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="960" windowWidth="21768" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="852" windowWidth="21768" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
   <si>
     <t>Password</t>
   </si>
@@ -215,63 +215,6 @@
     <t>0901234570</t>
   </si>
   <si>
-    <t>Test Case 1: Register User</t>
-  </si>
-  <si>
-    <t>1. Launch browser</t>
-  </si>
-  <si>
-    <t>2. Navigate to url 'http://automationexercise.com'</t>
-  </si>
-  <si>
-    <t>3. Verify that home page is visible successfully</t>
-  </si>
-  <si>
-    <t>4. Click on 'Signup / Login' button</t>
-  </si>
-  <si>
-    <t>5. Verify 'New User Signup!' is visible</t>
-  </si>
-  <si>
-    <t>6. Enter name and email address</t>
-  </si>
-  <si>
-    <t>7. Click 'Signup' button</t>
-  </si>
-  <si>
-    <t>8. Verify that 'ENTER ACCOUNT INFORMATION' is visible</t>
-  </si>
-  <si>
-    <t>9. Fill details: Title, Name, Email, Password, Date of birth</t>
-  </si>
-  <si>
-    <t>10. Select checkbox 'Sign up for our newsletter!'</t>
-  </si>
-  <si>
-    <t>11. Select checkbox 'Receive special offers from our partners!'</t>
-  </si>
-  <si>
-    <t>12. Fill details: First name, Last name, Company, Address, Address2, Country, State, City, Zipcode, Mobile Number</t>
-  </si>
-  <si>
-    <t>13. Click 'Create Account button'</t>
-  </si>
-  <si>
-    <t>14. Verify that 'ACCOUNT CREATED!' is visible</t>
-  </si>
-  <si>
-    <t>15. Click 'Continue' button</t>
-  </si>
-  <si>
-    <t>16. Verify that 'Logged in as username' is visible</t>
-  </si>
-  <si>
-    <t>17. Click 'Delete Account' button</t>
-  </si>
-  <si>
-    <t>18. Verify that 'ACCOUNT DELETED!' is visible and click 'Continue' button</t>
-  </si>
-  <si>
     <t>May</t>
   </si>
   <si>
@@ -282,13 +225,28 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>valid</t>
+  </si>
+  <si>
+    <t>invalid</t>
+  </si>
+  <si>
+    <t>qwee@gmail.com</t>
+  </si>
+  <si>
+    <t>https://automationexercise.com/test_cases#collapse1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,35 +277,12 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="16"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -406,7 +341,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -414,17 +349,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -731,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="1"/>
@@ -741,40 +667,59 @@
     <col min="5" max="5" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1231232131231</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>222</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1">
-        <v>123</v>
+        <v>123133122</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -783,15 +728,16 @@
     <hyperlink ref="B2" r:id="rId2" display="admin@123" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="A4" r:id="rId3" xr:uid="{509E6746-0179-4762-9083-E75C9AF220D4}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{E98AE939-4CA4-41CC-B36A-1121D2CA0B99}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{CF8D4D16-E15E-4657-8DBB-F708AE9F7CBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -876,40 +822,34 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K2" s="5"/>
       <c r="L2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>48</v>
@@ -918,111 +858,117 @@
         <v>49</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="I3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>49</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="J4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="L4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>49</v>
@@ -1031,27 +977,81 @@
         <v>52</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S5" s="5" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{D2CEBA7D-1D9E-4A65-96C1-EA297B87A456}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1103,114 +1103,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CBBA6-275A-4CE5-BBC4-47BBCE682D4F}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="F1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="4" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="8" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+    <row r="1" spans="6:6" s="7" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="45" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" location="collapse1" display="https://automationexercise.com/test_cases - collapse1" xr:uid="{F4CA735A-56AB-49DE-B228-7F12EA758942}"/>
-    <hyperlink ref="A3" r:id="rId2" display="https://automationexercise.com/" xr:uid="{41DA66A2-7A5C-49AC-AD64-111569E6E38D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC9162B-EA27-4EBA-9343-F1676C2C71D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9107D5-0A0F-42EB-93AC-9153615A553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="2148" windowWidth="23040" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="2148" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="87">
   <si>
     <t>Password</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>white</t>
+  </si>
+  <si>
+    <t>user_20260w402225_1901_a1@testmail.com</t>
   </si>
 </sst>
 </file>
@@ -845,7 +848,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -930,34 +933,40 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="J2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="L2" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>48</v>
@@ -966,57 +975,51 @@
         <v>49</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>48</v>
@@ -1025,111 +1028,117 @@
         <v>49</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="J5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="L5" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>49</v>
@@ -1138,28 +1147,82 @@
         <v>52</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="S6" s="5" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
-    <hyperlink ref="A2" r:id="rId4" xr:uid="{D2CEBA7D-1D9E-4A65-96C1-EA297B87A456}"/>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{D2CEBA7D-1D9E-4A65-96C1-EA297B87A456}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{A2606004-4F0F-4F89-884D-5EBAD941ACE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9107D5-0A0F-42EB-93AC-9153615A553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74796E8A-6939-4679-BE8B-E7560C4C7B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3780" yWindow="2148" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
-    <sheet name="AccountCreationData" sheetId="7" r:id="rId2"/>
-    <sheet name="ContactUsForm" sheetId="10" r:id="rId3"/>
-    <sheet name="SearchProduct" sheetId="6" r:id="rId4"/>
-    <sheet name="ProductDetails" sheetId="4" r:id="rId5"/>
+    <sheet name="ReviewData" sheetId="11" r:id="rId2"/>
+    <sheet name="AccountCreationData" sheetId="7" r:id="rId3"/>
+    <sheet name="ContactUsForm" sheetId="10" r:id="rId4"/>
+    <sheet name="SearchProduct" sheetId="6" r:id="rId5"/>
     <sheet name="Testcase" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="94">
   <si>
     <t>Password</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Product</t>
   </si>
   <si>
-    <t>qty</t>
-  </si>
-  <si>
     <t>t-shirt</t>
   </si>
   <si>
@@ -286,6 +283,30 @@
   </si>
   <si>
     <t>user_20260w402225_1901_a1@testmail.com</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Thoại</t>
+  </si>
+  <si>
+    <t>Joend</t>
+  </si>
+  <si>
+    <t>Lara</t>
+  </si>
+  <si>
+    <t>thanthaod22@gmail.com</t>
+  </si>
+  <si>
+    <t>thanthaod222222@gmail.com</t>
+  </si>
+  <si>
+    <t>Đồ này ok mặc vừa đẹp giá rẻ</t>
+  </si>
+  <si>
+    <t>Xấu quá</t>
   </si>
 </sst>
 </file>
@@ -447,7 +468,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -463,6 +484,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -786,51 +808,51 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1">
         <v>1231232131231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1">
         <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1">
         <v>123133122</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -847,6 +869,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A688CB-9FDF-4A0F-9B23-9EDBC11F3646}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="49.21875" customWidth="1"/>
+    <col min="3" max="3" width="62.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00F61BF3-783A-4981-8854-FD11F801CCC7}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{42328E72-1380-4872-B2D4-87434DCCC719}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -877,339 +973,339 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="O2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="S2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="O3" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="L4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="O4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="S4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="L5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="O6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="Q6" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="R6" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1226,85 +1322,85 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE416EC-5D80-4FBD-B182-45BC7F47C371}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -1321,7 +1417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1333,48 +1429,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>3</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1464,7 @@
     <row r="1" spans="6:6" s="7" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
